--- a/hoatdong.xlsx
+++ b/hoatdong.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/howl/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B352A60E-0540-0A45-BFA6-276A8ECB125E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBB3493-6182-2847-9D73-74ACFDBE61ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
   <si>
     <t>Nổi Bật</t>
   </si>
@@ -124,9 +124,6 @@
     <t>LXBC</t>
   </si>
   <si>
-    <t>Gửi Ảnh</t>
-  </si>
-  <si>
     <t>nhau.jpg</t>
   </si>
   <si>
@@ -151,7 +148,13 @@
     <t>Tư Liệu</t>
   </si>
   <si>
-    <t xml:space="preserve">gửi ảnh vào link </t>
+    <t>Đến</t>
+  </si>
+  <si>
+    <t>xem và gửi ảnh vào đây</t>
+  </si>
+  <si>
+    <t>lxbc</t>
   </si>
 </sst>
 </file>
@@ -615,7 +618,7 @@
         <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H2" t="s">
         <v>23</v>
@@ -644,7 +647,7 @@
         <v>19</v>
       </c>
       <c r="I3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -712,13 +715,13 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I7" t="s">
         <v>15</v>
@@ -735,19 +738,22 @@
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
         <v>43</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I8" t="s">
-        <v>34</v>
+        <v>42</v>
+      </c>
+      <c r="J8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="13:13" x14ac:dyDescent="0.2">
